--- a/histograms/histogram_d_A.xlsx
+++ b/histograms/histogram_d_A.xlsx
@@ -445,7 +445,7 @@
         <v>0.8699999999999999</v>
       </c>
       <c r="B2" t="n">
-        <v>2846</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>9.569999999999999</v>
       </c>
       <c r="B7" t="n">
-        <v>153</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>11.31</v>
       </c>
       <c r="B8" t="n">
-        <v>1622</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>13.05</v>
       </c>
       <c r="B9" t="n">
-        <v>10017</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>14.79</v>
       </c>
       <c r="B10" t="n">
-        <v>1803</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>16.53</v>
       </c>
       <c r="B11" t="n">
-        <v>3082</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>18.27</v>
       </c>
       <c r="B12" t="n">
-        <v>1737</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>20.01</v>
       </c>
       <c r="B13" t="n">
-        <v>852</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>21.75</v>
       </c>
       <c r="B14" t="n">
-        <v>312</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>23.48999999999999</v>
       </c>
       <c r="B15" t="n">
-        <v>821</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>25.23</v>
       </c>
       <c r="B16" t="n">
-        <v>1668</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>26.97</v>
       </c>
       <c r="B17" t="n">
-        <v>358</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>28.70999999999999</v>
       </c>
       <c r="B18" t="n">
-        <v>526</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -597,7 +597,7 @@
         <v>33.92999999999999</v>
       </c>
       <c r="B21" t="n">
-        <v>604</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
